--- a/data/samples/enrolment/Sir-Arthur-Lewis-Community-College.xlsx
+++ b/data/samples/enrolment/Sir-Arthur-Lewis-Community-College.xlsx
@@ -5,7 +5,8 @@
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
     <sheet name="Background" sheetId="2" r:id="rId2"/>
-    <sheet name="Enrolment" sheetId="3" r:id="rId3"/>
+    <sheet name="Finance" sheetId="3" r:id="rId3"/>
+    <sheet name="Enrolment" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -423,7 +424,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -444,15 +445,182 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>1.13 Does the institution have a strategic plan?</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Yes ☑  No ☐</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1.14 Does the institution have a Disaster Management Plan?</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Yes ☑  No ☐</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1.15 Emergency drills conducted in past year — how many?</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1.16 Are all areas accessible to students with disabilities?</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Yes ☑  No ☐</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1.17 Is the institution a member of the OECS NREN?</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Yes ☐  No ☑</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1.18 Number of teaching staff undertaking academic research (M / F)</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>T13. Revenue and Recurrent Expenditure</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>REVENUE</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="C3" t="str">
+        <v>RECURRENT EXPENDITURE</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Amount</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Government</v>
+      </c>
+      <c r="B4">
+        <v>6650000</v>
+      </c>
+      <c r="C4" t="str">
+        <v xml:space="preserve">  - Teaching Staff</v>
+      </c>
+      <c r="D4">
+        <v>3547500</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TOTAL</v>
+      </c>
+      <c r="B5">
+        <v>6650000</v>
+      </c>
+      <c r="C5" t="str">
+        <v>TOTAL</v>
+      </c>
+      <c r="D5">
+        <v>6450000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SDG 4.5.3 — Equity Funding Mechanism</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Does the institution have a formal mechanism to reallocate resources to disadvantaged groups?</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Yes ☑  No ☐</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>If yes, describe the mechanism</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Need-based bursaries and subsidised fees</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>What is the total value of equity-targeted funding in the previous academic year?</v>
+      </c>
+      <c r="B10">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SDG 4.c.5 — Average Teacher Salary Relative to Other Professions</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Average annual salary of full-time teaching staff (Local Currency):</v>
+      </c>
+      <c r="B13">
+        <v>68500</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Average annual salary of professions requiring comparable qualifications:</v>
+      </c>
+      <c r="B14">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Ratio (teacher salary ÷ comparator salary):</v>
+      </c>
+      <c r="B15">
+        <v>0.95</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:X13"/>
   <sheetData>
     <row r="1">
@@ -531,827 +699,827 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Business &amp; Management</v>
+        <v>Health Sciences</v>
       </c>
       <c r="B2" t="str">
-        <v>Bachelors</v>
+        <v>Diploma</v>
       </c>
       <c r="C2" t="str">
-        <v>Business Administration</v>
+        <v>Pharmacy Technician</v>
       </c>
       <c r="D2" t="str">
-        <v>Internationally</v>
+        <v>Regionally</v>
       </c>
       <c r="E2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
         <v>8</v>
       </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
       <c r="J2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Q2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="S2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="T2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Business &amp; Management</v>
+        <v>Health Sciences</v>
       </c>
       <c r="B3" t="str">
         <v>Associate Degree</v>
       </c>
       <c r="C3" t="str">
-        <v>Accounting</v>
+        <v>Medical Laboratory Technology</v>
       </c>
       <c r="D3" t="str">
         <v>Regionally</v>
       </c>
       <c r="E3" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <v>4</v>
+      </c>
+      <c r="P3">
+        <v>12</v>
+      </c>
+      <c r="Q3">
+        <v>22</v>
+      </c>
+      <c r="R3">
         <v>10</v>
       </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
-      <c r="O3">
-        <v>5</v>
-      </c>
-      <c r="P3">
-        <v>15</v>
-      </c>
-      <c r="Q3">
-        <v>28</v>
-      </c>
-      <c r="R3">
-        <v>12</v>
-      </c>
       <c r="S3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="T3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3">
         <v>3</v>
       </c>
       <c r="X3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Business &amp; Management</v>
+        <v>Information Technology</v>
       </c>
       <c r="B4" t="str">
-        <v>Diploma</v>
+        <v>Associate Degree</v>
       </c>
       <c r="C4" t="str">
-        <v>Marketing</v>
+        <v>Computer Science</v>
       </c>
       <c r="D4" t="str">
-        <v>Locally</v>
+        <v>Regionally</v>
       </c>
       <c r="E4" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F4">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>7</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
         <v>6</v>
       </c>
-      <c r="G4">
-        <v>11</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
-      <c r="N4">
-        <v>2</v>
-      </c>
       <c r="O4">
         <v>4</v>
       </c>
       <c r="P4">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="Q4">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="R4">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="S4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Health Sciences</v>
+        <v>Information Technology</v>
       </c>
       <c r="B5" t="str">
         <v>Bachelors</v>
       </c>
       <c r="C5" t="str">
-        <v>Nursing</v>
+        <v>Software Engineering</v>
       </c>
       <c r="D5" t="str">
         <v>Internationally</v>
       </c>
       <c r="E5" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <v>3</v>
+      </c>
+      <c r="P5">
+        <v>28</v>
+      </c>
+      <c r="Q5">
+        <v>13</v>
+      </c>
+      <c r="R5">
+        <v>23</v>
+      </c>
+      <c r="S5">
         <v>11</v>
       </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>9</v>
-      </c>
-      <c r="P5">
-        <v>7</v>
-      </c>
-      <c r="Q5">
-        <v>45</v>
-      </c>
-      <c r="R5">
-        <v>5</v>
-      </c>
-      <c r="S5">
-        <v>38</v>
-      </c>
       <c r="T5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="V5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X5">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Health Sciences</v>
+        <v>Humanities &amp; Education</v>
       </c>
       <c r="B6" t="str">
-        <v>Diploma</v>
+        <v>Bachelors</v>
       </c>
       <c r="C6" t="str">
-        <v>Pharmacy Technician</v>
+        <v>Primary Education</v>
       </c>
       <c r="D6" t="str">
-        <v>Regionally</v>
+        <v>Internationally</v>
       </c>
       <c r="E6" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
         <v>6</v>
       </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-      <c r="N6">
-        <v>2</v>
-      </c>
-      <c r="O6">
-        <v>5</v>
-      </c>
       <c r="P6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q6">
+        <v>30</v>
+      </c>
+      <c r="R6">
+        <v>5</v>
+      </c>
+      <c r="S6">
         <v>25</v>
       </c>
-      <c r="R6">
-        <v>9</v>
-      </c>
-      <c r="S6">
-        <v>21</v>
-      </c>
       <c r="T6">
         <v>2</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>1</v>
       </c>
       <c r="W6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Health Sciences</v>
+        <v>Humanities &amp; Education</v>
       </c>
       <c r="B7" t="str">
-        <v>Associate Degree</v>
+        <v>Certificate</v>
       </c>
       <c r="C7" t="str">
-        <v>Medical Laboratory Technology</v>
+        <v>Modern Languages</v>
       </c>
       <c r="D7" t="str">
-        <v>Regionally</v>
+        <v>Locally</v>
       </c>
       <c r="E7" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U7">
         <v>5</v>
       </c>
       <c r="V7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Information Technology</v>
+        <v>Humanities &amp; Education</v>
       </c>
       <c r="B8" t="str">
         <v>Associate Degree</v>
       </c>
       <c r="C8" t="str">
-        <v>Computer Science</v>
+        <v>Social Work</v>
       </c>
       <c r="D8" t="str">
         <v>Regionally</v>
       </c>
       <c r="E8" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <v>10</v>
       </c>
-      <c r="I8">
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>7</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>8</v>
+      </c>
+      <c r="Q8">
+        <v>28</v>
+      </c>
+      <c r="R8">
         <v>6</v>
       </c>
-      <c r="J8">
-        <v>7</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <v>3</v>
-      </c>
-      <c r="M8">
-        <v>2</v>
-      </c>
-      <c r="N8">
-        <v>6</v>
-      </c>
-      <c r="O8">
-        <v>3</v>
-      </c>
-      <c r="P8">
-        <v>28</v>
-      </c>
-      <c r="Q8">
-        <v>16</v>
-      </c>
-      <c r="R8">
-        <v>24</v>
-      </c>
       <c r="S8">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Information Technology</v>
+        <v>Hospitality &amp; Tourism</v>
       </c>
       <c r="B9" t="str">
-        <v>Bachelors</v>
+        <v>Diploma</v>
       </c>
       <c r="C9" t="str">
-        <v>Software Engineering</v>
+        <v>Culinary Arts</v>
       </c>
       <c r="D9" t="str">
-        <v>Internationally</v>
+        <v>Regionally</v>
       </c>
       <c r="E9" t="str">
         <v>Y</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P9">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Q9">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="R9">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="S9">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Humanities &amp; Education</v>
+        <v>Hospitality &amp; Tourism</v>
       </c>
       <c r="B10" t="str">
-        <v>Bachelors</v>
+        <v>Associate Degree</v>
       </c>
       <c r="C10" t="str">
-        <v>Primary Education</v>
+        <v>Hospitality Management</v>
       </c>
       <c r="D10" t="str">
-        <v>Internationally</v>
+        <v>Regionally</v>
       </c>
       <c r="E10" t="str">
         <v>N</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="R10">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="S10">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U10">
         <v>7</v>
       </c>
       <c r="V10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Humanities &amp; Education</v>
+        <v>Engineering &amp; Technology</v>
       </c>
       <c r="B11" t="str">
-        <v>Certificate</v>
+        <v>Associate Degree</v>
       </c>
       <c r="C11" t="str">
-        <v>Modern Languages</v>
+        <v>Civil Engineering</v>
       </c>
       <c r="D11" t="str">
-        <v>Locally</v>
+        <v>Regionally</v>
       </c>
       <c r="E11" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F11">
+        <v>15</v>
+      </c>
+      <c r="G11">
         <v>6</v>
       </c>
-      <c r="G11">
+      <c r="H11">
+        <v>11</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>4</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>6</v>
+      </c>
+      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="P11">
+        <v>32</v>
+      </c>
+      <c r="Q11">
+        <v>12</v>
+      </c>
+      <c r="R11">
+        <v>27</v>
+      </c>
+      <c r="S11">
         <v>10</v>
       </c>
-      <c r="H11">
-        <v>4</v>
-      </c>
-      <c r="I11">
-        <v>8</v>
-      </c>
-      <c r="J11">
-        <v>3</v>
-      </c>
-      <c r="K11">
-        <v>5</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>3</v>
-      </c>
-      <c r="N11">
-        <v>2</v>
-      </c>
-      <c r="O11">
-        <v>4</v>
-      </c>
-      <c r="P11">
-        <v>12</v>
-      </c>
-      <c r="Q11">
-        <v>22</v>
-      </c>
-      <c r="R11">
-        <v>10</v>
-      </c>
-      <c r="S11">
-        <v>18</v>
-      </c>
       <c r="T11">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Humanities &amp; Education</v>
+        <v>Engineering &amp; Technology</v>
       </c>
       <c r="B12" t="str">
-        <v>Associate Degree</v>
+        <v>Diploma</v>
       </c>
       <c r="C12" t="str">
-        <v>Social Work</v>
+        <v>Electrical Installation</v>
       </c>
       <c r="D12" t="str">
-        <v>Regionally</v>
+        <v>Locally</v>
       </c>
       <c r="E12" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>26</v>
+      </c>
+      <c r="Q12">
+        <v>4</v>
+      </c>
+      <c r="R12">
+        <v>22</v>
+      </c>
+      <c r="S12">
+        <v>4</v>
+      </c>
+      <c r="T12">
         <v>6</v>
       </c>
-      <c r="P12">
-        <v>9</v>
-      </c>
-      <c r="Q12">
-        <v>29</v>
-      </c>
-      <c r="R12">
-        <v>8</v>
-      </c>
-      <c r="S12">
-        <v>25</v>
-      </c>
-      <c r="T12">
-        <v>2</v>
-      </c>
       <c r="U12">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Hospitality &amp; Tourism</v>
+        <v>Engineering &amp; Technology</v>
       </c>
       <c r="B13" t="str">
-        <v>Diploma</v>
+        <v>Bachelors</v>
       </c>
       <c r="C13" t="str">
-        <v>Culinary Arts</v>
+        <v>Mechanical Engineering</v>
       </c>
       <c r="D13" t="str">
         <v>Regionally</v>
@@ -1360,61 +1528,61 @@
         <v>Y</v>
       </c>
       <c r="F13">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>7</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
         <v>6</v>
       </c>
-      <c r="G13">
+      <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>29</v>
+      </c>
+      <c r="Q13">
         <v>9</v>
       </c>
-      <c r="H13">
-        <v>5</v>
-      </c>
-      <c r="I13">
+      <c r="R13">
+        <v>25</v>
+      </c>
+      <c r="S13">
+        <v>8</v>
+      </c>
+      <c r="T13">
+        <v>7</v>
+      </c>
+      <c r="U13">
+        <v>2</v>
+      </c>
+      <c r="V13">
+        <v>3</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13">
         <v>6</v>
-      </c>
-      <c r="J13">
-        <v>3</v>
-      </c>
-      <c r="K13">
-        <v>4</v>
-      </c>
-      <c r="L13">
-        <v>2</v>
-      </c>
-      <c r="M13">
-        <v>2</v>
-      </c>
-      <c r="N13">
-        <v>3</v>
-      </c>
-      <c r="O13">
-        <v>3</v>
-      </c>
-      <c r="P13">
-        <v>13</v>
-      </c>
-      <c r="Q13">
-        <v>18</v>
-      </c>
-      <c r="R13">
-        <v>11</v>
-      </c>
-      <c r="S13">
-        <v>15</v>
-      </c>
-      <c r="T13">
-        <v>3</v>
-      </c>
-      <c r="U13">
-        <v>4</v>
-      </c>
-      <c r="V13">
-        <v>2</v>
-      </c>
-      <c r="W13">
-        <v>2</v>
-      </c>
-      <c r="X13">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
